--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260619_210314.xlsx
@@ -5928,7 +5928,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
